--- a/data/trans_dic/P36$nada-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36$nada-Edad-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no desayuna</t>
+          <t>Población que no desayuna (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 5,74</t>
+          <t>2,33; 5,69</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,95; 8,03</t>
+          <t>3,18; 7,98</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,86; 5,61</t>
+          <t>1,82; 5,54</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,41</t>
+          <t>2,58; 6,24</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,81; 6,98</t>
+          <t>2,82; 6,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,76</t>
+          <t>2,03; 5,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,73; 5,21</t>
+          <t>2,89; 5,36</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,57</t>
+          <t>3,44; 6,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 4,82</t>
+          <t>2,31; 4,99</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,17</t>
+          <t>0,49; 2,12</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,23; 7,0</t>
+          <t>3,28; 7,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,31; 5,17</t>
+          <t>2,19; 5,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 3,24</t>
+          <t>0,89; 3,32</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 5,18</t>
+          <t>1,88; 4,98</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 3,59</t>
+          <t>0,94; 3,37</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,86; 2,19</t>
+          <t>0,92; 2,27</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>3,08; 5,6</t>
+          <t>2,97; 5,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,83; 3,81</t>
+          <t>1,95; 3,93</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,69</t>
+          <t>0,8; 2,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,11</t>
+          <t>0,9; 3,44</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,91; 3,13</t>
+          <t>0,93; 3,27</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 2,59</t>
+          <t>0,69; 2,61</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,49</t>
+          <t>0,17; 1,41</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,82</t>
+          <t>0,41; 1,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 2,3</t>
+          <t>0,88; 2,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,92</t>
+          <t>0,62; 1,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,89; 2,24</t>
+          <t>0,85; 2,24</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,68; 5,02</t>
+          <t>1,58; 4,73</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,65</t>
+          <t>0,68; 2,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,38</t>
+          <t>0,96; 3,32</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,68</t>
+          <t>0,57; 2,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,5; 2,59</t>
+          <t>0,47; 2,55</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,92</t>
+          <t>0,0; 1,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,37; 3,44</t>
+          <t>1,33; 3,38</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,76; 2,16</t>
+          <t>0,75; 2,25</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,77</t>
+          <t>0,56; 1,87</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,02; 4,2</t>
+          <t>1,01; 4,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,75; 3,58</t>
+          <t>0,77; 3,44</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,78</t>
+          <t>0,21; 2,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,29</t>
+          <t>0,25; 2,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,41</t>
+          <t>0,73; 3,39</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,1</t>
+          <t>0,0; 1,11</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,87; 2,61</t>
+          <t>0,9; 2,71</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,88</t>
+          <t>1,03; 2,87</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,56</t>
+          <t>0,11; 1,53</t>
         </is>
       </c>
     </row>
@@ -1233,42 +1233,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,14</t>
+          <t>0,3; 2,97</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,74</t>
+          <t>0,0; 1,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,56</t>
+          <t>0,0; 1,49</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,59</t>
+          <t>0,0; 1,8</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,37</t>
+          <t>0,0; 1,36</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,31</t>
+          <t>0,14; 1,41</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 1,81</t>
+          <t>0,31; 2,02</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,85</t>
+          <t>0,0; 0,86</t>
         </is>
       </c>
     </row>
@@ -1338,37 +1338,37 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,01</t>
+          <t>0,82; 4,88</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,86</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,15</t>
+          <t>0,0; 1,99</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,42</t>
+          <t>0,0; 1,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,64</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,46; 2,19</t>
+          <t>0,43; 2,24</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,32</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,64; 2,63</t>
+          <t>1,59; 2,62</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,09; 3,27</t>
+          <t>2,02; 3,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,46; 2,46</t>
+          <t>1,47; 2,48</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,03</t>
+          <t>1,17; 2,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,27</t>
+          <t>1,31; 2,21</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,72; 1,39</t>
+          <t>0,71; 1,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,52; 2,21</t>
+          <t>1,53; 2,19</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,82; 2,57</t>
+          <t>1,8; 2,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,81</t>
+          <t>1,17; 1,72</t>
         </is>
       </c>
     </row>
@@ -1543,7 +1543,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que no desayuna</t>
+          <t>Población que no desayuna (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11454; 28316</t>
+          <t>11474; 28085</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>13420; 36488</t>
+          <t>14445; 36262</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7786; 23546</t>
+          <t>7622; 23219</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12723; 29965</t>
+          <t>12064; 29182</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12013; 29887</t>
+          <t>12061; 28890</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8302; 22738</t>
+          <t>8007; 23332</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>26198; 50076</t>
+          <t>27721; 51480</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30326; 57930</t>
+          <t>30374; 57437</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19000; 39219</t>
+          <t>18830; 40623</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3625; 15975</t>
+          <t>3589; 15613</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22193; 48048</t>
+          <t>22494; 48156</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>13654; 30549</t>
+          <t>12915; 30867</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5338; 20200</t>
+          <t>5556; 20717</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11895; 31543</t>
+          <t>11478; 30316</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5562; 20240</t>
+          <t>5272; 19002</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>11661; 29759</t>
+          <t>12545; 30783</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>39926; 72475</t>
+          <t>38484; 72965</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>21146; 44012</t>
+          <t>22483; 45380</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4794; 17080</t>
+          <t>5062; 17969</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>5791; 21140</t>
+          <t>6116; 23332</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6066; 20922</t>
+          <t>6192; 21850</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4270; 17862</t>
+          <t>4791; 17988</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1071; 10567</t>
+          <t>1177; 10027</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2705; 12051</t>
+          <t>2707; 12784</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>12253; 30483</t>
+          <t>11639; 30738</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9330; 26622</t>
+          <t>8656; 25157</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11855; 29840</t>
+          <t>11360; 29779</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8711; 25970</t>
+          <t>8179; 24454</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4157; 16241</t>
+          <t>4184; 17761</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6074; 21768</t>
+          <t>6194; 21396</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2974; 13758</t>
+          <t>2932; 13203</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3063; 15940</t>
+          <t>2890; 15740</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 5951</t>
+          <t>0; 6879</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14135; 35492</t>
+          <t>13715; 34863</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9378; 26595</t>
+          <t>9267; 27720</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7261; 22905</t>
+          <t>7264; 24098</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3931; 16251</t>
+          <t>3898; 15450</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3236; 15392</t>
+          <t>3323; 14776</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1012; 13305</t>
+          <t>1023; 13224</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1008; 9235</t>
+          <t>992; 10010</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3175; 15227</t>
+          <t>3246; 15148</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5488</t>
+          <t>0; 5501</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>6852; 20666</t>
+          <t>7133; 21439</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8565; 25243</t>
+          <t>9029; 25165</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1985; 15186</t>
+          <t>1107; 14926</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>848; 7226</t>
+          <t>849; 7219</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1106; 9721</t>
+          <t>917; 9199</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5824</t>
+          <t>0; 5482</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 5360</t>
+          <t>0; 5109</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 9168</t>
+          <t>0; 6370</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5168</t>
+          <t>0; 5128</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>897; 8332</t>
+          <t>898; 8937</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2090; 12022</t>
+          <t>2090; 13417</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6018</t>
+          <t>0; 6110</t>
         </is>
       </c>
     </row>
@@ -2728,47 +2728,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1783; 10507</t>
+          <t>1714; 10244</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 2150</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1627</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 7187</t>
+          <t>0; 6641</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5512</t>
+          <t>0; 5844</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0; 2544</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2487; 11921</t>
+          <t>2356; 12199</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 5494</t>
+          <t>0; 5469</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0; 2090</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>53617; 86118</t>
+          <t>52059; 85648</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>71506; 111914</t>
+          <t>68931; 110026</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>49617; 83495</t>
+          <t>49710; 84215</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>40235; 68593</t>
+          <t>39420; 69792</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>46793; 80458</t>
+          <t>46694; 78507</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>25658; 49321</t>
+          <t>25221; 49154</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>100811; 146599</t>
+          <t>101491; 145377</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>126625; 179043</t>
+          <t>125629; 183500</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>80945; 125550</t>
+          <t>81086; 119229</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P36$nada-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P36$nada-Edad-trans_dic.xlsx
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,33; 5,69</t>
+          <t>2,3; 5,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3,18; 7,98</t>
+          <t>3,13; 7,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,54</t>
+          <t>1,83; 5,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,58; 6,24</t>
+          <t>2,7; 6,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,82; 6,75</t>
+          <t>2,68; 6,56</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 5,91</t>
+          <t>2,01; 5,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>2,89; 5,36</t>
+          <t>2,82; 5,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,44; 6,51</t>
+          <t>3,38; 6,69</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,31; 4,99</t>
+          <t>2,28; 4,99</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,12</t>
+          <t>0,51; 2,23</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>3,28; 7,02</t>
+          <t>3,26; 7,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,19; 5,23</t>
+          <t>2,31; 5,23</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,89; 3,32</t>
+          <t>0,95; 3,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 4,98</t>
+          <t>1,96; 5,21</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,94; 3,37</t>
+          <t>0,95; 3,55</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,92; 2,27</t>
+          <t>0,85; 2,18</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,97; 5,63</t>
+          <t>3,09; 5,65</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>1,95; 3,93</t>
+          <t>1,91; 3,79</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,83</t>
+          <t>0,75; 2,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,44</t>
+          <t>0,85; 3,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,27</t>
+          <t>0,93; 3,36</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,69; 2,61</t>
+          <t>0,69; 2,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 1,41</t>
+          <t>0,15; 1,49</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 1,93</t>
+          <t>0,42; 1,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 2,32</t>
+          <t>0,89; 2,2</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,81</t>
+          <t>0,66; 1,96</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 2,24</t>
+          <t>0,81; 2,32</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>1,58; 4,73</t>
+          <t>1,68; 4,88</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,68; 2,89</t>
+          <t>0,69; 2,76</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,96; 3,32</t>
+          <t>0,86; 3,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,57</t>
+          <t>0,58; 2,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,55</t>
+          <t>0,51; 2,8</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,06</t>
+          <t>0,0; 1,02</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,33; 3,38</t>
+          <t>1,32; 3,34</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,75; 2,25</t>
+          <t>0,69; 2,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,56; 1,87</t>
+          <t>0,53; 1,77</t>
         </is>
       </c>
     </row>
@@ -1118,27 +1118,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,01; 4,0</t>
+          <t>1,04; 4,1</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,77; 3,44</t>
+          <t>0,76; 3,46</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,21; 2,77</t>
+          <t>0,22; 2,9</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,25; 2,48</t>
+          <t>0,25; 2,47</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>0,73; 3,39</t>
+          <t>0,71; 3,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1148,17 +1148,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,9; 2,71</t>
+          <t>0,87; 2,62</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>1,03; 2,87</t>
+          <t>0,98; 2,88</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,53</t>
+          <t>0,19; 1,52</t>
         </is>
       </c>
     </row>
@@ -1233,42 +1233,42 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,97</t>
+          <t>0,32; 3,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,64</t>
+          <t>0,0; 1,73</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,49</t>
+          <t>0,0; 1,45</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,8</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,36</t>
+          <t>0,0; 1,7</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,41</t>
+          <t>0,14; 1,38</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,31; 2,02</t>
+          <t>0,32; 1,95</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,86</t>
+          <t>0,0; 0,92</t>
         </is>
       </c>
     </row>
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,82; 4,88</t>
+          <t>0,84; 4,98</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,99</t>
+          <t>0,0; 1,98</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,5</t>
+          <t>0,0; 1,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>0,43; 2,24</t>
+          <t>0,4; 2,41</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,59; 2,62</t>
+          <t>1,6; 2,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,02; 3,22</t>
+          <t>2,09; 3,28</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,48</t>
+          <t>1,47; 2,44</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 2,07</t>
+          <t>1,22; 2,14</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>1,31; 2,21</t>
+          <t>1,32; 2,23</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,71; 1,39</t>
+          <t>0,7; 1,38</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>1,53; 2,19</t>
+          <t>1,53; 2,17</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,63</t>
+          <t>1,83; 2,57</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>1,17; 1,72</t>
+          <t>1,17; 1,74</t>
         </is>
       </c>
     </row>
@@ -1750,47 +1750,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>11474; 28085</t>
+          <t>11348; 27336</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>14445; 36262</t>
+          <t>14209; 34189</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7622; 23219</t>
+          <t>7670; 23112</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12064; 29182</t>
+          <t>12630; 29797</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>12061; 28890</t>
+          <t>11477; 28082</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8007; 23332</t>
+          <t>7941; 23304</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27721; 51480</t>
+          <t>27082; 50508</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>30374; 57437</t>
+          <t>29810; 59061</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>18830; 40623</t>
+          <t>18533; 40651</t>
         </is>
       </c>
     </row>
@@ -1913,47 +1913,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>3589; 15613</t>
+          <t>3745; 16373</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>22494; 48156</t>
+          <t>22369; 49061</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12915; 30867</t>
+          <t>13612; 30894</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5556; 20717</t>
+          <t>5914; 20224</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>11478; 30316</t>
+          <t>11965; 31712</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5272; 19002</t>
+          <t>5365; 20024</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>12545; 30783</t>
+          <t>11561; 29577</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>38484; 72965</t>
+          <t>40076; 73166</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>22483; 45380</t>
+          <t>22006; 43689</t>
         </is>
       </c>
     </row>
@@ -2076,47 +2076,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5062; 17969</t>
+          <t>4787; 17306</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6116; 23332</t>
+          <t>5794; 20894</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6192; 21850</t>
+          <t>6255; 22486</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4791; 17988</t>
+          <t>4787; 17843</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>1177; 10027</t>
+          <t>1070; 10549</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2707; 12784</t>
+          <t>2767; 13029</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>11639; 30738</t>
+          <t>11780; 29089</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>8656; 25157</t>
+          <t>9097; 27250</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>11360; 29779</t>
+          <t>10838; 30912</t>
         </is>
       </c>
     </row>
@@ -2239,47 +2239,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8179; 24454</t>
+          <t>8690; 25231</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4184; 17761</t>
+          <t>4210; 16942</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6194; 21396</t>
+          <t>5522; 21436</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2932; 13203</t>
+          <t>2968; 13191</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2890; 15740</t>
+          <t>3123; 17227</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0; 6879</t>
+          <t>0; 6640</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13715; 34863</t>
+          <t>13565; 34484</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9267; 27720</t>
+          <t>8468; 27074</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>7264; 24098</t>
+          <t>6806; 22879</t>
         </is>
       </c>
     </row>
@@ -2402,47 +2402,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3898; 15450</t>
+          <t>4010; 15862</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3323; 14776</t>
+          <t>3249; 14869</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1023; 13224</t>
+          <t>1028; 13850</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>992; 10010</t>
+          <t>1015; 9971</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3246; 15148</t>
+          <t>3185; 14832</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0; 5501</t>
+          <t>0; 5493</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7133; 21439</t>
+          <t>6874; 20713</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>9029; 25165</t>
+          <t>8598; 25241</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1107; 14926</t>
+          <t>1869; 14780</t>
         </is>
       </c>
     </row>
@@ -2565,47 +2565,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>849; 7219</t>
+          <t>839; 7226</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>917; 9199</t>
+          <t>991; 9525</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5482</t>
+          <t>0; 5791</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 5109</t>
+          <t>0; 4972</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 6370</t>
+          <t>0; 6265</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>0; 5128</t>
+          <t>0; 6427</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>898; 8937</t>
+          <t>896; 8796</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2090; 13417</t>
+          <t>2102; 12945</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0; 6110</t>
+          <t>0; 6516</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>1714; 10244</t>
+          <t>1772; 10456</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2743,12 +2743,12 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>0; 6641</t>
+          <t>0; 6605</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>0; 5844</t>
+          <t>0; 6163</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2758,12 +2758,12 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>2356; 12199</t>
+          <t>2153; 13086</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>0; 5469</t>
+          <t>0; 5482</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
@@ -2891,47 +2891,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>52059; 85648</t>
+          <t>52434; 84976</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>68931; 110026</t>
+          <t>71506; 112203</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>49710; 84215</t>
+          <t>49934; 82559</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>39420; 69792</t>
+          <t>41150; 72259</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>46694; 78507</t>
+          <t>47040; 79044</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>25221; 49154</t>
+          <t>24758; 48971</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>101491; 145377</t>
+          <t>101631; 144151</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>125629; 183500</t>
+          <t>127785; 179095</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>81086; 119229</t>
+          <t>81435; 120669</t>
         </is>
       </c>
     </row>
